--- a/Zerde_ZhI_frazeologizm/Tazhiribe_kestesi.xlsx
+++ b/Zerde_ZhI_frazeologizm/Tazhiribe_kestesi.xlsx
@@ -1323,14 +1323,32 @@
           <t>қатты қуану</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="7" t="n"/>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>қатты қуану, мәз болып күлу деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G2" s="7" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="7" t="n"/>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>адамның өте қуанышты, мәз-мейрам болған күйін, яғни қатты күлуін, қуаныштан аузы құлағына жеткендей болуын білдіреді.</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J2" s="7" t="n"/>
-      <c r="K2" s="6" t="n"/>
-      <c r="L2" s="7" t="n"/>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>Бұл тұрақты тіркес адамның қатты қуанғанын, мәз болып, шаттанғанын білдіреді (адам қатты күлгенде немесе жымиғанда аузының езуі кең созылатынына негізделген).</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M2" s="7" t="n"/>
     </row>
     <row r="3" ht="45" customHeight="1">
@@ -1352,14 +1370,32 @@
           <t>өкінді</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="7" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>қатты өкінді деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G3" s="7" t="n"/>
-      <c r="H3" s="6" t="n"/>
-      <c r="I3" s="7" t="n"/>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>адамның қатты өкінгенін, амалсыздан қынжылғанын, я болмаса бір нәрсеге таңырқап, таңдай қаққанын білдіреді. Көбінесе өкініш, өшпенділік немесе қызығушылық мәнінде қолданылады.</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J3" s="7" t="n"/>
-      <c r="K3" s="6" t="n"/>
-      <c r="L3" s="7" t="n"/>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Бұл тұрақты тіркес жіберіп алған мүмкіндікке немесе жасаған қателігіне қатты өкінуді, өкініш білдіруді білдіреді.</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M3" s="7" t="n"/>
     </row>
     <row r="4" ht="45" customHeight="1">
@@ -1381,14 +1417,32 @@
           <t>өте тез</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="7" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>өте тез, қас қағым сәтте деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G4" s="7" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="7" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>тіркес өте қысқа уақытты, лезде, тез болғандықты білдіреді. Яғни бір нәрсенің көз ашып-жұмған аралығындай жылдам жүзеге асқанын сипаттайды.</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J4" s="7" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="7" t="n"/>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>іс-әрекеттің өте жылдам, лезде, қас-қағым сәтте орын алғанын білдіреді.</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M4" s="7" t="n"/>
     </row>
     <row r="5" ht="45" customHeight="1">
@@ -1410,14 +1464,32 @@
           <t>үндемеу, сөйлемеу</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="7" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>үндемеу, ештеңе айтпау деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G5" s="7" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="7" t="n"/>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>үндемеу, ешнәрсе айтпау, сыр бермеу деген мағынаны білдіреді. Адамның тапжылмай үнсіз қалуын, тіс жарып сөйлемеуін сипаттайды.</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J5" s="7" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="7" t="n"/>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>ештеңе айтпауды, мүлдем үндемеуді, тіс жармауды немесе сырды берік сақтауды білдіреді.</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M5" s="7" t="n"/>
     </row>
     <row r="6" ht="45" customHeight="1">
@@ -1439,14 +1511,32 @@
           <t>мұқият тыңдау, назар салу</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="7" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>зейін қойып, мұқият тыңдау деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G6" s="7" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="7" t="n"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>бір нәрсеге қатты назар аудару, мұқият тыңдау, сақ болу деген мағынаны білдіреді. Көбінесе «құлақ түру» түрінде де қолданылады.</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J6" s="7" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="7" t="n"/>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>бірдеңені мұқият, зейін қойып тыңдауды немесе қандай да бір жаңалықты, хабарды күтіп елеңдеуді білдіреді.</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M6" s="7" t="n"/>
     </row>
     <row r="7" ht="45" customHeight="1">
@@ -1468,14 +1558,32 @@
           <t>ұйықтамау</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="n"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>ұйықтамау, көз ілмеу деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G7" s="7" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="7" t="n"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>ұйықтамау, көз ілмеу, түні бойы ояу болу деген мағынаны білдіреді. Сондай-ақ бір нәрсеге қатты көңіл бөліп, көз алмай қарау мәнінде де қолданылады.</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J7" s="7" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="7" t="n"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>мүлдем ұйықтамауды, көз ілмеуді немесе бір нәрсеге өте мұқият, тапжылмай назар аударуды білдіреді (көбіне түні бойы ұйықтамай шығу мағынасында қолданылады).</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M7" s="7" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
@@ -1497,14 +1605,32 @@
           <t>қатты толқыды, қорықты</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="7" t="n"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>қатты қорықты, шошыды деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G8" s="7" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="7" t="n"/>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>қатты қорыққанда, үрейленгенде немесе қатты толқығанда жүректің соғуы жиілеп, дүрсілдеп кетуін білдіреді. Яғни адамның қорқыныш немесе қобалжу күйін сипаттайды.</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J8" s="7" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="7" t="n"/>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>кенеттен қатты қорқуды, үрейленуді, зәресі ұшуды білдіреді.</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M8" s="7" t="n"/>
     </row>
     <row r="9" ht="45" customHeight="1">
@@ -1526,15 +1652,41 @@
           <t>келісті</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="7" t="n"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>келіскенін, мақұлдағанын білдірді деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="7" t="n"/>
-      <c r="J9" s="7" t="n"/>
-      <c r="K9" s="6" t="n"/>
-      <c r="L9" s="7" t="n"/>
-      <c r="M9" s="7" t="n"/>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>келісім білдіру, мақұлдау, «иә» деп жауап беру деген мағынаны білдіреді. Сондай-ақ біреуге бағыныштылық, мойынсұну мәнінде де қолданылады.</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>келісуді, мақұлдауды, рұқсат беруді немесе үнсіз амандасу белгісін білдіреді.</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="4" t="n">
@@ -1555,14 +1707,32 @@
           <t>жомарт</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="7" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>жомарт, барын өзгелерден аямайтын деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="7" t="n"/>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>жомарт, береген, сараң емес адамды сипаттайды. Яғни адамның қолынан келгенінше көмектесетін, сый-сияпат жасауға дайын жомарт мінезін білдіреді.</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J10" s="7" t="n"/>
-      <c r="K10" s="6" t="n"/>
-      <c r="L10" s="7" t="n"/>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>жомарт, мырза, қолында барын басқалардан аямайтын, қайырымды адамды білдіреді.</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M10" s="7" t="n"/>
     </row>
     <row r="11" ht="45" customHeight="1">
@@ -1584,14 +1754,36 @@
           <t>қатты ұялды</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="7" t="n"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>қатты ұялды, ұялғаннан беті қызарды деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="7" t="n"/>
-      <c r="J11" s="7" t="n"/>
-      <c r="K11" s="6" t="n"/>
-      <c r="L11" s="7" t="n"/>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t>адамның қатты ұялғанын, қызарып кеткенін, ұятқа қалғанын білдіреді. Кейде қатты ызаланған, ашуланған күйін де сипаттайды.</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>қатты ұялуды, қысылуды немесе ыңғайсыз жағдайда қалып, беті дуылдап қызаруды білдіреді.</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M11" s="7" t="n"/>
     </row>
     <row r="12" ht="45" customHeight="1">
@@ -1613,14 +1805,32 @@
           <t>өте тату</t>
         </is>
       </c>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="7" t="n"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>өте тату, бір-біріне жақын деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="7" t="n"/>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>екі адамның өте жақын, тығыз қарым-қатынаста екенін, араларына ешкімнің кіріге алмайтынын білдіреді. Сондай-ақ бір нәрсенің тығыз, мызғымас, берік екенін сипаттауда да қолданылады.</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J12" s="7" t="n"/>
-      <c r="K12" s="6" t="n"/>
-      <c r="L12" s="7" t="n"/>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>екі адамның арасындағы өте тығыз достықты, айырылмас татулықты, сыйластық пен бірлікті білдіреді.</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M12" s="7" t="n"/>
     </row>
     <row r="13" ht="45" customHeight="1">
@@ -1642,14 +1852,32 @@
           <t>момын, жуас</t>
         </is>
       </c>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="7" t="n"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>өте жуас, момын, ешкімге зияны жоқ деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G13" s="7" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="7" t="n"/>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>өте момын, жуас, жұмсақ мінезді, ешкімге зияны жоқ адамды сипаттайды. Яғни адамның ұрыспайтын, ашуланбайтын, мүлдем зиянсыз, көнбіс мінезін білдіреді.</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J13" s="7" t="n"/>
-      <c r="K13" s="6" t="n"/>
-      <c r="L13" s="7" t="n"/>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>өте момын, жуас, ешкімге залалы тимейтін, тыныш әрі бейуаз адамды білдіреді.</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M13" s="7" t="n"/>
     </row>
     <row r="14" ht="45" customHeight="1">
@@ -1671,14 +1899,32 @@
           <t>лық толы, бос орын жоқ</t>
         </is>
       </c>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="7" t="n"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>адам өте көп, бос орын жоқ деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G14" s="7" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="7" t="n"/>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>адамның өте тығыз, лық толы, көпшілік қаумалаған жағдайын білдіреді. Яғни айналада бос орын жоқ, адамдар тым көп деген мағынаны білдіреді.</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J14" s="7" t="n"/>
-      <c r="K14" s="6" t="n"/>
-      <c r="L14" s="7" t="n"/>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>орынның өте лық толы екенін, бос жер мүлдем жоқ екенін немесе халықтың шектен тыс көп жиналғанын білдіреді.</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M14" s="7" t="n"/>
     </row>
     <row r="15" ht="45" customHeight="1">
@@ -1700,14 +1946,32 @@
           <t>өте қиын, ауыр, ұзақ іс</t>
         </is>
       </c>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="7" t="n"/>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>көп еңбекті, шыдамдылық пен табандылықты қажет ететін қиын істі білдіретін тұрақты тіркес.</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G15" s="7" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="7" t="n"/>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>Ол өте ауыр, азапты, ұзақ әрі нәтижесіз немесе асқан шыдамдылықты қажет ететін жұмыс деген мағынаны білдіреді</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J15" s="7" t="n"/>
-      <c r="K15" s="6" t="n"/>
-      <c r="L15" s="7" t="n"/>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>өте үлкен сабырды, төзімділікті, ұқыптылықты және қажырлы еңбекті талап ететін аса қиын әрі баяу жүретін істі сипаттайтын бейнелі тіркес</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M15" s="7" t="n"/>
     </row>
     <row r="16" ht="45" customHeight="1">
@@ -1729,14 +1993,32 @@
           <t>қатты ұялу</t>
         </is>
       </c>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="7" t="n"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>қатты ұялу, қысылу, ұялғаннан тығылар жер таппау деген мағынаны білдіретін тұрақты тіркес.</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="7" t="n"/>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>қатты ұялып, не істерін білмей қалу, «жерге кіріп кетердей болу» дегенді білдіреді</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J16" s="7" t="n"/>
-      <c r="K16" s="6" t="n"/>
-      <c r="L16" s="7" t="n"/>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>қатты ұялғаннан, айыпты болғаннан немесе ыңғайсыз жағдайға тап болғаннан жасырынатын жер таппай, не істерін білмей сасқалақтауды білдіретін тұрақты тіркес.</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M16" s="7" t="n"/>
     </row>
     <row r="17" ht="45" customHeight="1">
@@ -1758,14 +2040,32 @@
           <t>тар, кішкентай жер</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="7" t="n"/>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>көлемі өте кішкентай, шағын деген мағына</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="7" t="n"/>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>«өте шағын, тар, кішкентай» дегенді білдіреді</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J17" s="7" t="n"/>
-      <c r="K17" s="6" t="n"/>
-      <c r="L17" s="7" t="n"/>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>аумағы немесе көлемі өте шағын, кішкентай, тұтастай көзге сиып тұратын жерді, орынды немесе затты сипаттайтын тұрақты тіркес.</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M17" s="7" t="n"/>
     </row>
     <row r="18" ht="45" customHeight="1">
@@ -1787,14 +2087,32 @@
           <t>тып-тыныш</t>
         </is>
       </c>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="7" t="n"/>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>тым-тырыс, ешбір дыбыс естілмейтін тыныштық</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="7" t="n"/>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>«тып-тыныш, жым-жырт», яғни айналада ешбір дыбыс естілмейтін, мүлдем тыныштық орнаған күйді білдіреді</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J18" s="7" t="n"/>
-      <c r="K18" s="6" t="n"/>
-      <c r="L18" s="7" t="n"/>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>айналада ешқандай дыбыс, дабыра жоқ, айналаның жым-жырт, тып-тыныш болып мүлгіп тұрған күйін білдіретін тұрақты тіркес.</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M18" s="7" t="n"/>
     </row>
     <row r="19" ht="45" customHeight="1">
@@ -1816,14 +2134,32 @@
           <t>үндемейтін адам</t>
         </is>
       </c>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="7" t="n"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>үндемей, ештеңе айтпай отыру</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="7" t="n"/>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>«үндемейтін адам, ауыз ашпайтын, сөйлемейтін адам»</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J19" s="7" t="n"/>
-      <c r="K19" s="6" t="n"/>
-      <c r="L19" s="7" t="n"/>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>ештеңе айтпай, мүлдем сөйлемей, сұрақтарға жауап бермей ләм-мим демей отырып алу</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M19" s="7" t="n"/>
     </row>
     <row r="20" ht="45" customHeight="1">
@@ -1845,14 +2181,32 @@
           <t>батыр, қорықпайтын</t>
         </is>
       </c>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="7" t="n"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>өте батыл, ержүрек, ештеңеден қорықпайтын адам</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="7" t="n"/>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>«батыр, ержүрек, ешнәрседен қорықпайтын адам»</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J20" s="7" t="n"/>
-      <c r="K20" s="6" t="n"/>
-      <c r="L20" s="7" t="n"/>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>ештеңеден қорықпайтын, қауіп-қатерге қаймықпай қарсы тұратын, өте батыл, өжет әрі қайсар адам</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M20" s="7" t="n"/>
     </row>
     <row r="21" ht="45" customHeight="1">
@@ -1874,14 +2228,32 @@
           <t>қу, айлакер</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="7" t="n"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>болмашы нәрседен де пайда табуға тырысатын, айлакер, қу адам</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="7" t="n"/>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>«тым сараң, қу, пайдакүнем»</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J21" s="7" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="7" t="n"/>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>өте сараң, тым есепшіл, ешқандай мүмкіндік жоқ жерден де пайда тапқысы келетін шектен шыққан дүниеқоңыз, ашқарақ адам</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M21" s="7" t="n"/>
     </row>
     <row r="22" ht="45" customHeight="1">
@@ -1903,14 +2275,32 @@
           <t>хан сайлады</t>
         </is>
       </c>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="7" t="n"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>хан сайлады</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="7" t="n"/>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>хан көтерді, таққа отырғызды</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J22" s="7" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="7" t="n"/>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>хан етіп сайлады, ел басшысы етіп ұлықтады немесе бір адамға ерекше құрмет көрсетіп, жоғары дәрежеге көтерді</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M22" s="7" t="n"/>
     </row>
     <row r="23" ht="45" customHeight="1">
@@ -1932,14 +2322,32 @@
           <t>жолы болды</t>
         </is>
       </c>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="7" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>жолы болды, ісі оңға басты, сәттілікке жетті</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="7" t="n"/>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>ісі оңға басты, сәті түсті, жолы болды</t>
+        </is>
+      </c>
+      <c r="I23" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J23" s="7" t="n"/>
-      <c r="K23" s="6" t="n"/>
-      <c r="L23" s="7" t="n"/>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>ісі оңға басып, бағы жанды, жолы болып, сәттілікке кенелді</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M23" s="7" t="n"/>
     </row>
     <row r="24" ht="45" customHeight="1">
@@ -1961,14 +2369,32 @@
           <t>молшылық орнау</t>
         </is>
       </c>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="7" t="n"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>молшылыққа кенелу, ішіп-жемнің ағыл-тегіл көп болуы</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="7" t="n"/>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>молшылық, береке, тоқшылық орнау</t>
+        </is>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J24" s="7" t="n"/>
-      <c r="K24" s="6" t="n"/>
-      <c r="L24" s="7" t="n"/>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>тұрмыс-тіршілікте азық-түлік, мал-жан, ақ (сүт өнімдері) өте мол болып, шалқыған тоқшылық пен береке орнаған кез</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M24" s="7" t="n"/>
     </row>
     <row r="25" ht="45" customHeight="1">
@@ -1990,14 +2416,32 @@
           <t>тыныш, бейбіт заман орнау</t>
         </is>
       </c>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="7" t="n"/>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>елде тыныштық, бейбітшілік пен молшылық орнау</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G25" s="7" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="7" t="n"/>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t>бейбіт, тыныш, молшылық заман орнау</t>
+        </is>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J25" s="7" t="n"/>
-      <c r="K25" s="6" t="n"/>
-      <c r="L25" s="7" t="n"/>
+      <c r="K25" s="6" t="inlineStr">
+        <is>
+          <t>елде толық тыныштық пен бейбітшілік орнаған, ешқандай қауіп-қатерсіз, мамыражай, берекелі де тоқ заман</t>
+        </is>
+      </c>
+      <c r="L25" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M25" s="7" t="n"/>
     </row>
     <row r="26" ht="45" customHeight="1">
@@ -2019,15 +2463,37 @@
           <t>баю</t>
         </is>
       </c>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="7" t="n"/>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>баю, шалқып, молшылықта өмір сүру</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G26" s="7" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="7" t="n"/>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>баю, дәулеті асу, байып кету</t>
+        </is>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J26" s="7" t="n"/>
-      <c r="K26" s="6" t="n"/>
-      <c r="L26" s="7" t="n"/>
-      <c r="M26" s="7" t="n"/>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>аяқастынан ашуға міну, шамдану, мінез көрсетіп, тулап шыға келу</t>
+        </is>
+      </c>
+      <c r="L26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>О</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="45" customHeight="1">
       <c r="A27" s="4" t="n">
@@ -2048,14 +2514,32 @@
           <t>қатты ұрысу, балағаттау</t>
         </is>
       </c>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="7" t="n"/>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>қатты ұрысу, балағаттау, жер-жебіріне жету</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G27" s="7" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="7" t="n"/>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>қатты ұрысу, балағаттау, сөгу</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J27" s="7" t="n"/>
-      <c r="K27" s="6" t="n"/>
-      <c r="L27" s="7" t="n"/>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>бір адамды аямай қатты ұрсу, жер-жебіріне жету, ауыр сөздер айтып, жерден алып жерге салу</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M27" s="7" t="n"/>
     </row>
     <row r="28" ht="45" customHeight="1">
@@ -2077,15 +2561,41 @@
           <t>алдау</t>
         </is>
       </c>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="7" t="n"/>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="7" t="n"/>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>жеңу, жеңіліске ұшырату</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>О</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t>алдау, алаяқтық жасау</t>
+        </is>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J28" s="7" t="n"/>
-      <c r="K28" s="6" t="n"/>
-      <c r="L28" s="7" t="n"/>
-      <c r="M28" s="7" t="n"/>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>біреуді ойсырата жеңу, айласын асырып сүріндіру немесе тиісті сазайын беріп, сағын сындыру</t>
+        </is>
+      </c>
+      <c r="L28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>О</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="45" customHeight="1">
       <c r="A29" s="4" t="n">
@@ -2106,14 +2616,32 @@
           <t>өте алыс жер</t>
         </is>
       </c>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="7" t="n"/>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>өте алыс, шалғай жер</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G29" s="7" t="n"/>
-      <c r="H29" s="6" t="n"/>
-      <c r="I29" s="7" t="n"/>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t>тым алыс, қашық, қияндағы жер</t>
+        </is>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J29" s="7" t="n"/>
-      <c r="K29" s="6" t="n"/>
-      <c r="L29" s="7" t="n"/>
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>өте алыстағы, жетуі қиын, шеткері, адам аяғы сирек басатын немесе елсіз, қаңырап қалған шалғай аймақ</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M29" s="7" t="n"/>
     </row>
     <row r="30" ht="45" customHeight="1">
@@ -2135,14 +2663,36 @@
           <t>асқақтап, дәурен сүру</t>
         </is>
       </c>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="7" t="n"/>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>жолы болып, бағы жану, дәурені жүру</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G30" s="7" t="n"/>
-      <c r="H30" s="6" t="n"/>
-      <c r="I30" s="7" t="n"/>
-      <c r="J30" s="7" t="n"/>
-      <c r="K30" s="6" t="n"/>
-      <c r="L30" s="7" t="n"/>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t>мақтанып, тәкаппарлану, өзін жоғары санау</t>
+        </is>
+      </c>
+      <c r="I30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>О</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>бағы жанып, ісі оңға басып, абыройы мен мерейі тасып, өркендеп тұрған немесе еңсесі көтеріңкі күй</t>
+        </is>
+      </c>
+      <c r="L30" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M30" s="7" t="n"/>
     </row>
     <row r="31" ht="45" customHeight="1">
@@ -2164,14 +2714,32 @@
           <t>масқаралау, ел алдында ұятқа қалдыру</t>
         </is>
       </c>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="7" t="n"/>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>ел алдында масқаралау, мазақ ету, абыройын төгу</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="6" t="n"/>
-      <c r="I31" s="7" t="n"/>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t>артына кір келтіру, ұятқа қалдыру, масқаралау</t>
+        </is>
+      </c>
+      <c r="I31" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J31" s="7" t="n"/>
-      <c r="K31" s="6" t="n"/>
-      <c r="L31" s="7" t="n"/>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>біреудің абыройын айрандай төгіп, ел алдында масқаралау, қатты жазалау немесе беделін жұрт алдында мүлдем түсіру</t>
+        </is>
+      </c>
+      <c r="L31" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M31" s="7" t="n"/>
     </row>
   </sheetData>
@@ -2298,14 +2866,32 @@
           <t>Беті бүлк етпеді (ұялды – ұялмады)</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="7" t="n"/>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>«Беті бүлк етпеді» — ұялмады, қысылмады</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G2" s="7" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="7" t="n"/>
+      <c r="H2" s="6" t="inlineStr">
+        <is>
+          <t>беті бүлк етпеді</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J2" s="7" t="n"/>
-      <c r="K2" s="6" t="n"/>
-      <c r="L2" s="7" t="n"/>
+      <c r="K2" s="6" t="inlineStr">
+        <is>
+          <t>Беті бүлк етпеу</t>
+        </is>
+      </c>
+      <c r="L2" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M2" s="7" t="n"/>
     </row>
     <row r="3" ht="40" customHeight="1">
@@ -2327,15 +2913,41 @@
           <t>Қуанышы қойнына сыймады (мұңайды – қуанды)</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n"/>
-      <c r="F3" s="7" t="n"/>
-      <c r="G3" s="7" t="n"/>
-      <c r="H3" s="6" t="n"/>
-      <c r="I3" s="7" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>«Ажары кірді» — өңі жақсарды, көріктене түсті</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="H3" s="6" t="inlineStr">
+        <is>
+          <t>«қуанышы қойнына сыймады» (қуаныштан іші-бауыры қызу, қатты қуану) тіркесі</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J3" s="7" t="n"/>
-      <c r="K3" s="6" t="n"/>
-      <c r="L3" s="7" t="n"/>
-      <c r="M3" s="7" t="n"/>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>Жүзіне қан жүгіру</t>
+        </is>
+      </c>
+      <c r="L3" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="7" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="40" customHeight="1">
       <c r="A4" s="4" t="n">
@@ -2356,14 +2968,32 @@
           <t>Саусағының ұшын қимылдатпады (тез қимылдады – ештеңе істемеді)</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="7" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>«Қол қусырып отырды» — ештеңе істемеді, әрекетсіз отырды</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G4" s="7" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="7" t="n"/>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Саусағының ұшын қимылдатпады</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J4" s="7" t="n"/>
-      <c r="K4" s="6" t="n"/>
-      <c r="L4" s="7" t="n"/>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>Саусағының ұшын да қимылдатпау</t>
+        </is>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M4" s="7" t="n"/>
     </row>
     <row r="5" ht="40" customHeight="1">
@@ -2385,14 +3015,36 @@
           <t>Қыздың жиған жүгіндей (сұлу, әдемі)</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n"/>
-      <c r="F5" s="7" t="n"/>
-      <c r="G5" s="7" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="7" t="n"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>«Ай десе аузы, күн десе көзі бар» — өте сұлу, көрікті</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Ж</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Қыздың жиған жүгіндей</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J5" s="7" t="n"/>
-      <c r="K5" s="6" t="n"/>
-      <c r="L5" s="7" t="n"/>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Сұлулығына көз сүрінеді</t>
+        </is>
+      </c>
+      <c r="L5" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M5" s="7" t="n"/>
     </row>
     <row r="6" ht="40" customHeight="1">
@@ -2414,14 +3066,32 @@
           <t>Ит арқасы қиянда; Жер түбі (алыс, шалғай)</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n"/>
-      <c r="F6" s="7" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>«Ит арқасы қиянда» — өте алыс, шалғайда</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G6" s="7" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="7" t="n"/>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>Ит арқасы қиян</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J6" s="7" t="n"/>
-      <c r="K6" s="6" t="n"/>
-      <c r="L6" s="7" t="n"/>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>Ит арқасы қиянда</t>
+        </is>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M6" s="7" t="n"/>
     </row>
     <row r="7" ht="40" customHeight="1">
@@ -2443,14 +3113,33 @@
           <t>Жерден алып, жерге салды (ұрысты, сөкті)</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="7" t="n"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>«Жер-жебіріне жетті» — қатты ұрысты,</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="G7" s="7" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="7" t="n"/>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t>«жерден алып, жерге салды» — ұрысты, сөкті</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="J7" s="7" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="7" t="n"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>Жер-жебіріне жету
+Жерден алып, жерге салу</t>
+        </is>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>2</v>
+      </c>
       <c r="M7" s="7" t="n"/>
     </row>
     <row r="9">
@@ -2544,11 +3233,23 @@
       <c r="B2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C2" s="6" t="n"/>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Көзді ашып-жұмғанша</t>
+        </is>
+      </c>
       <c r="D2" s="7" t="n"/>
-      <c r="E2" s="6" t="n"/>
+      <c r="E2" s="6" t="inlineStr">
+        <is>
+          <t>Көзді ашып-жұмғанша</t>
+        </is>
+      </c>
       <c r="F2" s="7" t="n"/>
-      <c r="G2" s="6" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
+        <is>
+          <t>Көзді ашып-жұмғанша</t>
+        </is>
+      </c>
       <c r="H2" s="7" t="n"/>
     </row>
     <row r="3">
@@ -2556,11 +3257,23 @@
       <c r="B3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="6" t="n"/>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Қас пен көздің арасында</t>
+        </is>
+      </c>
       <c r="D3" s="7" t="n"/>
-      <c r="E3" s="6" t="n"/>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Қас пен көздің арасында</t>
+        </is>
+      </c>
       <c r="F3" s="7" t="n"/>
-      <c r="G3" s="6" t="n"/>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>Қас пен көздің арасында</t>
+        </is>
+      </c>
       <c r="H3" s="7" t="n"/>
     </row>
     <row r="4">
@@ -2568,11 +3281,23 @@
       <c r="B4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="6" t="n"/>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Кірпік қаққанша</t>
+        </is>
+      </c>
       <c r="D4" s="7" t="n"/>
-      <c r="E4" s="6" t="n"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Аяғы аяғына жұқпады</t>
+        </is>
+      </c>
       <c r="F4" s="7" t="n"/>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Аяғы аяғына тимеу</t>
+        </is>
+      </c>
       <c r="H4" s="7" t="n"/>
     </row>
     <row r="5">
@@ -2580,11 +3305,27 @@
       <c r="B5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="7" t="n"/>
-      <c r="E5" s="6" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Әп дегенше</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Т</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Қас қағымда</t>
+        </is>
+      </c>
       <c r="F5" s="7" t="n"/>
-      <c r="G5" s="6" t="n"/>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Оқтай атылу</t>
+        </is>
+      </c>
       <c r="H5" s="7" t="n"/>
     </row>
     <row r="6">
@@ -2592,11 +3333,23 @@
       <c r="B6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="6" t="n"/>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Аяқ-аяғына жұқпау</t>
+        </is>
+      </c>
       <c r="D6" s="7" t="n"/>
-      <c r="E6" s="6" t="n"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Ерні ерніне тимеді</t>
+        </is>
+      </c>
       <c r="F6" s="7" t="n"/>
-      <c r="G6" s="6" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>Желдей есу</t>
+        </is>
+      </c>
       <c r="H6" s="7" t="n"/>
     </row>
     <row r="7">
@@ -2608,11 +3361,23 @@
       <c r="B7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="6" t="n"/>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Ит өлген жер</t>
+        </is>
+      </c>
       <c r="D7" s="7" t="n"/>
-      <c r="E7" s="6" t="n"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Ит өлген жер</t>
+        </is>
+      </c>
       <c r="F7" s="7" t="n"/>
-      <c r="G7" s="6" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>Ит өлген жер</t>
+        </is>
+      </c>
       <c r="H7" s="7" t="n"/>
     </row>
     <row r="8">
@@ -2620,11 +3385,23 @@
       <c r="B8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="6" t="n"/>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Ит арқасы қиянда</t>
+        </is>
+      </c>
       <c r="D8" s="7" t="n"/>
-      <c r="E8" s="6" t="n"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Ит арқасы қиянда</t>
+        </is>
+      </c>
       <c r="F8" s="7" t="n"/>
-      <c r="G8" s="6" t="n"/>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>Ит арқасы қиянда</t>
+        </is>
+      </c>
       <c r="H8" s="7" t="n"/>
     </row>
     <row r="9">
@@ -2632,11 +3409,23 @@
       <c r="B9" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="6" t="n"/>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Жердің түбі</t>
+        </is>
+      </c>
       <c r="D9" s="7" t="n"/>
-      <c r="E9" s="6" t="n"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Қиянның қиынында</t>
+        </is>
+      </c>
       <c r="F9" s="7" t="n"/>
-      <c r="G9" s="6" t="n"/>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>Жердің түбінде</t>
+        </is>
+      </c>
       <c r="H9" s="7" t="n"/>
     </row>
     <row r="10">
@@ -2644,11 +3433,23 @@
       <c r="B10" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="6" t="n"/>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Жер мойны қашық</t>
+        </is>
+      </c>
       <c r="D10" s="7" t="n"/>
-      <c r="E10" s="6" t="n"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Ат тұяғы тимеген</t>
+        </is>
+      </c>
       <c r="F10" s="7" t="n"/>
-      <c r="G10" s="6" t="n"/>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>Ат табаны жетпейтін жер</t>
+        </is>
+      </c>
       <c r="H10" s="7" t="n"/>
     </row>
     <row r="11">
@@ -2656,12 +3457,32 @@
       <c r="B11" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="6" t="n"/>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Айшылық алыс жер</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>Т</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Қиыр шет</t>
+        </is>
+      </c>
       <c r="F11" s="7" t="n"/>
-      <c r="G11" s="6" t="n"/>
-      <c r="H11" s="7" t="n"/>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>Айшылық жер</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>Т</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -2672,11 +3493,23 @@
       <c r="B12" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C12" s="6" t="n"/>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Таяқ тастам жер</t>
+        </is>
+      </c>
       <c r="D12" s="7" t="n"/>
-      <c r="E12" s="6" t="n"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>қол созым жер</t>
+        </is>
+      </c>
       <c r="F12" s="7" t="n"/>
-      <c r="G12" s="6" t="n"/>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>Таяқ тастам жер</t>
+        </is>
+      </c>
       <c r="H12" s="7" t="n"/>
     </row>
     <row r="13">
@@ -2684,11 +3517,23 @@
       <c r="B13" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C13" s="6" t="n"/>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Қарға адым жер</t>
+        </is>
+      </c>
       <c r="D13" s="7" t="n"/>
-      <c r="E13" s="6" t="n"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>көз жететін жер</t>
+        </is>
+      </c>
       <c r="F13" s="7" t="n"/>
-      <c r="G13" s="6" t="n"/>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>Қол созым жер</t>
+        </is>
+      </c>
       <c r="H13" s="7" t="n"/>
     </row>
     <row r="14">
@@ -2696,11 +3541,27 @@
       <c r="B14" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C14" s="6" t="n"/>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Қол созым жер</t>
+        </is>
+      </c>
       <c r="D14" s="7" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="7" t="n"/>
-      <c r="G14" s="6" t="n"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>үш қайнаса сорпасы қосылмайтын</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>М</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>Екі адым жер</t>
+        </is>
+      </c>
       <c r="H14" s="7" t="n"/>
     </row>
     <row r="15">
@@ -2708,23 +3569,59 @@
       <c r="B15" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="7" t="n"/>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Иек астында</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>Т</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>ат құлағында ойнайтын</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>М</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>Мұрын түбінде (немесе Мұрын астында)</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>Т</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="n"/>
       <c r="B16" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Тиіп тұр</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>Т</t>
+        </is>
+      </c>
       <c r="E16" s="6" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="6" t="n"/>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>Ат аттам жер</t>
+        </is>
+      </c>
       <c r="H16" s="7" t="n"/>
     </row>
     <row r="17">
@@ -2736,11 +3633,23 @@
       <c r="B17" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C17" s="6" t="n"/>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Құмырсқадай құжынаған</t>
+        </is>
+      </c>
       <c r="D17" s="7" t="n"/>
-      <c r="E17" s="6" t="n"/>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Қарасы қалың</t>
+        </is>
+      </c>
       <c r="F17" s="7" t="n"/>
-      <c r="G17" s="6" t="n"/>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>Ине шаншар жер жоқ</t>
+        </is>
+      </c>
       <c r="H17" s="7" t="n"/>
     </row>
     <row r="18">
@@ -2748,23 +3657,51 @@
       <c r="B18" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C18" s="6" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Қара құрым</t>
+        </is>
+      </c>
       <c r="D18" s="7" t="n"/>
-      <c r="E18" s="6" t="n"/>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Қалың қол</t>
+        </is>
+      </c>
       <c r="F18" s="7" t="n"/>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="7" t="n"/>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>Қара ормандай</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>Т</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="n"/>
       <c r="B19" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C19" s="6" t="n"/>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Ине шаншар жер жоқ</t>
+        </is>
+      </c>
       <c r="D19" s="7" t="n"/>
-      <c r="E19" s="6" t="n"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Қалың бұқара</t>
+        </is>
+      </c>
       <c r="F19" s="7" t="n"/>
-      <c r="G19" s="6" t="n"/>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>Құмырсқадай өру</t>
+        </is>
+      </c>
       <c r="H19" s="7" t="n"/>
     </row>
     <row r="20">
@@ -2772,11 +3709,31 @@
       <c r="B20" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="7" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="7" t="n"/>
-      <c r="G20" s="6" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Құмдай көп</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Т</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Бір кісідей бар екен</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Т</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>Иін тіресу</t>
+        </is>
+      </c>
       <c r="H20" s="7" t="n"/>
     </row>
     <row r="21">
@@ -2784,11 +3741,27 @@
       <c r="B21" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C21" s="6" t="n"/>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Жер қайысқан қол</t>
+        </is>
+      </c>
       <c r="D21" s="7" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="7" t="n"/>
-      <c r="G21" s="6" t="n"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Ел-жұрттың қарасы қалың</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Т</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>Қара құрттай қаптау</t>
+        </is>
+      </c>
       <c r="H21" s="7" t="n"/>
     </row>
     <row r="22">
@@ -2800,11 +3773,23 @@
       <c r="B22" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="C22" s="6" t="n"/>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Қас қарая</t>
+        </is>
+      </c>
       <c r="D22" s="7" t="n"/>
-      <c r="E22" s="6" t="n"/>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Қас қарайды</t>
+        </is>
+      </c>
       <c r="F22" s="7" t="n"/>
-      <c r="G22" s="6" t="n"/>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>Қас қарайғанда</t>
+        </is>
+      </c>
       <c r="H22" s="7" t="n"/>
     </row>
     <row r="23">
@@ -2812,11 +3797,27 @@
       <c r="B23" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C23" s="6" t="n"/>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Көз байлана</t>
+        </is>
+      </c>
       <c r="D23" s="7" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="7" t="n"/>
-      <c r="G23" s="6" t="n"/>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Күн батты</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Т</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Көз байланғанда</t>
+        </is>
+      </c>
       <c r="H23" s="7" t="n"/>
     </row>
     <row r="24">
@@ -2824,11 +3825,23 @@
       <c r="B24" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="C24" s="6" t="n"/>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>Екі кештің арасында</t>
+        </is>
+      </c>
       <c r="D24" s="7" t="n"/>
-      <c r="E24" s="6" t="n"/>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>Ымырт үйірілді</t>
+        </is>
+      </c>
       <c r="F24" s="7" t="n"/>
-      <c r="G24" s="6" t="n"/>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>Ел орынға отыра</t>
+        </is>
+      </c>
       <c r="H24" s="7" t="n"/>
     </row>
     <row r="25">
@@ -2836,11 +3849,23 @@
       <c r="B25" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="C25" s="6" t="n"/>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>Ел орынға отыра</t>
+        </is>
+      </c>
       <c r="D25" s="7" t="n"/>
-      <c r="E25" s="6" t="n"/>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>Ақшам түсті</t>
+        </is>
+      </c>
       <c r="F25" s="7" t="n"/>
-      <c r="G25" s="6" t="n"/>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>Алакеуім шақта</t>
+        </is>
+      </c>
       <c r="H25" s="7" t="n"/>
     </row>
     <row r="26">
@@ -2848,11 +3873,27 @@
       <c r="B26" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="C26" s="6" t="n"/>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>Күн ұясына кіргенде</t>
+        </is>
+      </c>
       <c r="D26" s="7" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="7" t="n"/>
-      <c r="G26" s="6" t="n"/>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>Түн ортасы</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Т</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>Ақшам түсе</t>
+        </is>
+      </c>
       <c r="H26" s="7" t="n"/>
     </row>
   </sheetData>
@@ -2902,7 +3943,11 @@
           <t>ЖИ-1</t>
         </is>
       </c>
-      <c r="B2" s="6" t="n"/>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>ChatGPT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -2910,7 +3955,11 @@
           <t>ЖИ-2</t>
         </is>
       </c>
-      <c r="B3" s="6" t="n"/>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>DeepSeek</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -2918,7 +3967,11 @@
           <t>ЖИ-3</t>
         </is>
       </c>
-      <c r="B4" s="6" t="n"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Gemini</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
